--- a/out/Attention-S4_repeat_1_000007.xlsx
+++ b/out/Attention-S4_repeat_1_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.3291019071641194</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.3291019071641194</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.3291019071641194</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.3291019071641194</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.3291019071641194</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.1769695850834732</v>
+        <v>2.815552302146115</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1769695850834732</v>
+        <v>2.815552302146115</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.1769695850834732</v>
+        <v>2.815552302146115</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001134953702826751</v>
+        <v>-0.0003147087108066771</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.308433921786554</v>
+        <v>3.628126564976986</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.1769695850834732</v>
+        <v>2.815552302146115</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.618890597840206</v>
+        <v>7.261861710415421</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1962055032020286</v>
+        <v>0.5440537853671716</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.70111147806619</v>
+        <v>4.716973119755734</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.2453207201446305</v>
+        <v>0.6802441986218356</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.415552302146115</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.995578642158548</v>
+        <v>5.533494244743925</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.3516660889179379</v>
+        <v>0.975126832733186</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.453728757377077</v>
+        <v>6.803887815684718</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.3762130571988894</v>
+        <v>1.043192558111079</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.854515373775298</v>
+        <v>7.915219174204441</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3987107491237636</v>
+        <v>1.105573846399234</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC45" t="n">
-        <v>3.27575158679499</v>
+        <v>9.083254027806262</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1799307455481719</v>
+        <v>0.4989255804238026</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.236571001719125</v>
+        <v>8.974611138061292</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.08689768292522884</v>
+        <v>0.240958251182039</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.230295819031545</v>
+        <v>8.957210834171565</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04140477170071296</v>
+        <v>0.1148088200088956</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.226137383353662</v>
+        <v>8.945680095471497</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01226669755136253</v>
+        <v>0.03401741571677653</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.209223150336709</v>
+        <v>8.898782586714075</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008111778934528645</v>
+        <v>0.02250077149188195</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.213175848009251</v>
+        <v>8.909749913777562</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.004149258505810741</v>
+        <v>0.01151514651492945</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.213357781505486</v>
+        <v>8.910263234763045</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002120063772178579</v>
+        <v>0.00588800015269228</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.213446202030221</v>
+        <v>8.910517235551868</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007942704725452334</v>
+        <v>0.002210402152594601</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.21291206181583</v>
+        <v>8.909045575128074</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004306031559925421</v>
+        <v>0.001201983744729335</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.212978552404017</v>
+        <v>8.909238731835748</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002048087069473987</v>
+        <v>0.0005767423238086963</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.212957291219964</v>
+        <v>8.909188644007237</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001248820755014253</v>
+        <v>0.0003551275729812248</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.213002148555289</v>
+        <v>8.909321884800637</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>6.29383643940398e-05</v>
+        <v>0.0001833745558198376</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.213003067746046</v>
+        <v>8.909333297102283</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.797007331591087e-05</v>
+        <v>8.591747490145118e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.212996026995535</v>
+        <v>8.909322639265742</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.546634204420339e-05</v>
+        <v>5.384073337708474e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.213000255014693</v>
+        <v>8.90934336370039</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>4.324890221093473e-06</v>
+        <v>2.180905938564374e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.212993311269625</v>
+        <v>8.9093331022389</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-8.825233700581938e-07</v>
+        <v>6.323060732339969e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.212987078607376</v>
+        <v>8.909324951127878</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>1.675769385467227e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.212982492697843</v>
+        <v>8.909320943321967</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-2.093548687745288e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.212977059566375</v>
+        <v>8.909315075879283</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.212972012945307</v>
+        <v>8.909310006523915</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.212972331225524</v>
+        <v>8.909305641549947</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.21297342247198</v>
+        <v>8.909306732796402</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.212972732864845</v>
+        <v>8.909306043189266</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.212972763177247</v>
+        <v>8.90930607350167</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.212972573724736</v>
+        <v>8.909305884049159</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.21297262677144</v>
+        <v>8.909305937095862</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.212972679818142</v>
+        <v>8.909305990142563</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.21297264192764</v>
+        <v>8.909305952252062</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.212972513099933</v>
+        <v>8.909305823424356</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.212972369116026</v>
+        <v>8.909305679440449</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.212972209975918</v>
+        <v>8.90930552030034</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.21297226302262</v>
+        <v>8.909305573347043</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.212972209975918</v>
+        <v>8.90930552030034</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.212972209975918</v>
+        <v>8.90930552030034</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.212972028101508</v>
+        <v>8.909305338425931</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.212972194819717</v>
+        <v>8.90930550514414</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.212972391850327</v>
+        <v>8.909305702174748</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.212972232710219</v>
+        <v>8.909305543034641</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.21297227060072</v>
+        <v>8.909305580925142</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.212972467631331</v>
+        <v>8.909305777955753</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.21297244489703</v>
+        <v>8.909305755221453</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.212972293335021</v>
+        <v>8.909305603659444</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.212972217554018</v>
+        <v>8.909305527878441</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.212972316069324</v>
+        <v>8.909305626393746</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.212972323647424</v>
+        <v>8.909305633971845</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.212972588880938</v>
+        <v>8.909305899205359</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.212972293335021</v>
+        <v>8.909305603659444</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.212972535834234</v>
+        <v>8.909305846158658</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.212972619193339</v>
+        <v>8.90930592951776</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.21297245247513</v>
+        <v>8.909305762799551</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.21297264192764</v>
+        <v>8.909305952252062</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.212972293335021</v>
+        <v>8.909305603659444</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.212972088726311</v>
+        <v>8.909305399050734</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.212972202397817</v>
+        <v>8.90930551272224</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.212972217554018</v>
+        <v>8.909305527878441</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.212971982632906</v>
+        <v>8.909305292957328</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.212972043257709</v>
+        <v>8.90930535358213</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.212971914430002</v>
+        <v>8.909305224754425</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.21297205083581</v>
+        <v>8.909305361160232</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.212972225132118</v>
+        <v>8.909305535456539</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.212972369116026</v>
+        <v>8.909305679440449</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.212972202397817</v>
+        <v>8.90930551272224</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.212972194819717</v>
+        <v>8.90930550514414</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.212971906851902</v>
+        <v>8.909305217176323</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.212971922008103</v>
+        <v>8.909305232332525</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.212972149351114</v>
+        <v>8.909305459675537</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.212972134194913</v>
+        <v>8.909305444519335</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.212972240288319</v>
+        <v>8.909305550612743</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.212971967476705</v>
+        <v>8.909305277801126</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.21297206599201</v>
+        <v>8.909305376316432</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.212972217554018</v>
+        <v>8.909305527878441</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.212972232710219</v>
+        <v>8.909305543034641</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.212972209975918</v>
+        <v>8.90930552030034</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.212972293335021</v>
+        <v>8.909305603659444</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.212972391850327</v>
+        <v>8.909305702174748</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.212972225132118</v>
+        <v>8.909305535456539</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.212972209975918</v>
+        <v>8.90930552030034</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.212972179663516</v>
+        <v>8.909305489987938</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.212972164507315</v>
+        <v>8.909305474831738</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.212972202397817</v>
+        <v>8.90930551272224</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.212972217554018</v>
+        <v>8.909305527878441</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.212972209975918</v>
+        <v>8.90930552030034</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_1_000007.xlsx
+++ b/out/Attention-S4_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001134953702826751</v>
+        <v>-0.0001218910279163392</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.308433921786554</v>
+        <v>1.405223454710736</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.618890597840206</v>
+        <v>2.812619282838985</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1962055032020286</v>
+        <v>0.2107195254203982</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.70111147806619</v>
+        <v>1.826948769710943</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.2453207201446305</v>
+        <v>0.2634679704750115</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.995578642158548</v>
+        <v>2.14319871717364</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.3516660889179379</v>
+        <v>0.3776800862049891</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.453728757377077</v>
+        <v>2.635239817932465</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.3762130571988894</v>
+        <v>0.4040432295089283</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.854515373775298</v>
+        <v>3.065674024568085</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3987107491237636</v>
+        <v>0.4282043845947278</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC45" t="n">
-        <v>3.27575158679499</v>
+        <v>3.518070138195614</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1799307455481719</v>
+        <v>0.193240008828056</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.236571001719125</v>
+        <v>3.475991267850171</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.08689768292522884</v>
+        <v>0.09332673509398459</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.230295819031545</v>
+        <v>3.469251869868549</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04140477170071296</v>
+        <v>0.04446679786296001</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.226137383353662</v>
+        <v>3.464785842855833</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01226669755136253</v>
+        <v>0.01317423205557543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.209223150336709</v>
+        <v>3.446620613382627</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008111778934528645</v>
+        <v>0.008712558995409792</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.213175848009251</v>
+        <v>3.450866230787483</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.004149258505810741</v>
+        <v>0.004457236457567908</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.213357781505486</v>
+        <v>3.451061998268621</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002120063772178579</v>
+        <v>0.002277103065622377</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.213446202030221</v>
+        <v>3.451157320761765</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007942704725452334</v>
+        <v>0.0008533074960855064</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.21291206181583</v>
+        <v>3.450584096326991</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004306031559925421</v>
+        <v>0.0004627783891056276</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.212978552404017</v>
+        <v>3.450655867469989</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002048087069473987</v>
+        <v>0.0002199085760080069</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.212957291219964</v>
+        <v>3.450633405661045</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001248820755014253</v>
+        <v>0.0001347216266757757</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.213002148555289</v>
+        <v>3.450682040067227</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>6.29383643940398e-05</v>
+        <v>6.808521018146706e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.213003067746046</v>
+        <v>3.450683407681526</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.797007331591087e-05</v>
+        <v>2.996825957748122e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.212996026995535</v>
+        <v>3.450676212936765</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.546634204420339e-05</v>
+        <v>1.802463479972881e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.213000255014693</v>
+        <v>3.450681279019888</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>4.324890221093473e-06</v>
+        <v>5.490501498730158e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.212993311269625</v>
+        <v>3.450674220187132</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.212987078607376</v>
+        <v>3.450667987524883</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.212982492697843</v>
+        <v>3.45066340161535</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.212977059566375</v>
+        <v>3.450657968483882</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.212972012945307</v>
+        <v>3.450652921862814</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.212972331225524</v>
+        <v>3.450653240143031</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383072</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.21297342247198</v>
+        <v>3.450654331389488</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-4.409276425334539</v>
+        <v>-1.809504746419567</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.212972732864845</v>
+        <v>3.450653641782352</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-4.409276425334539</v>
+        <v>-2.857789548800827</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.212972763177247</v>
+        <v>3.450653672094754</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-4.409276425334539</v>
+        <v>-1.809504746419567</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.212972573724736</v>
+        <v>3.450653482642243</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383072</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.21297262677144</v>
+        <v>3.450653535688947</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.212972679818142</v>
+        <v>3.45065358873565</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.21297264192764</v>
+        <v>3.450653550845147</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.212972513099933</v>
+        <v>3.45065342201744</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.212972369116026</v>
+        <v>3.450653278033533</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.212972209975918</v>
+        <v>3.450653118893425</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.5612199440383071</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.21297226302262</v>
+        <v>3.450653171940127</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.5612199440383071</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.212972209975918</v>
+        <v>3.450653118893425</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383072</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.212972209975918</v>
+        <v>3.450653118893425</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.212972028101508</v>
+        <v>3.450652937019016</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.212972194819717</v>
+        <v>3.450653103737224</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.212972391850327</v>
+        <v>3.450653300767834</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.212972232710219</v>
+        <v>3.450653141627726</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.21297227060072</v>
+        <v>3.450653179518227</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.212972467631331</v>
+        <v>3.450653376548838</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.21297244489703</v>
+        <v>3.450653353814537</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.212972293335021</v>
+        <v>3.450653202252528</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.212972217554018</v>
+        <v>3.450653126471525</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.212972316069324</v>
+        <v>3.450653224986831</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.212972323647424</v>
+        <v>3.450653232564931</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.212972588880938</v>
+        <v>3.450653497798445</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.212972293335021</v>
+        <v>3.450653202252528</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.212972535834234</v>
+        <v>3.450653444751741</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.212972619193339</v>
+        <v>3.450653528110846</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.21297245247513</v>
+        <v>3.450653361392638</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.21297264192764</v>
+        <v>3.450653550845147</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383072</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.212972293335021</v>
+        <v>3.450653202252528</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-4.409276425334539</v>
+        <v>-1.809504746419567</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.212972088726311</v>
+        <v>3.450652997643818</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-4.409276425334539</v>
+        <v>-1.809504746419567</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.212972202397817</v>
+        <v>3.450653111315324</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383072</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.212972217554018</v>
+        <v>3.450653126471525</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.212971982632906</v>
+        <v>3.450652891550413</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.212972043257709</v>
+        <v>3.450652952175216</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.212971914430002</v>
+        <v>3.450652823347509</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.21297205083581</v>
+        <v>3.450652959753317</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.212972225132118</v>
+        <v>3.450653134049625</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.212972369116026</v>
+        <v>3.450653278033533</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.212972202397817</v>
+        <v>3.450653111315324</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7769695850834732</v>
+        <v>-0.5612199440383071</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.212972194819717</v>
+        <v>3.450653103737224</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-4.409276425334539</v>
+        <v>-0.7612199440383072</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.212971906851902</v>
+        <v>3.450652815769409</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383072</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.212971922008103</v>
+        <v>3.45065283092561</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.212972149351114</v>
+        <v>3.450653058268621</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.2870648583429531</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.212972134194913</v>
+        <v>3.45065304311242</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.212972240288319</v>
+        <v>3.450653149205826</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.212971967476705</v>
+        <v>3.450652876394212</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.21297206599201</v>
+        <v>3.450652974909517</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.212972217554018</v>
+        <v>3.450653126471525</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.212972232710219</v>
+        <v>3.450653141627726</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.212972209975918</v>
+        <v>3.450653118893425</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383072</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.212972293335021</v>
+        <v>3.450653202252528</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-4.409276425334539</v>
+        <v>-1.809504746419567</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.212972391850327</v>
+        <v>3.450653300767834</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-4.409276425334539</v>
+        <v>-2.857789548800827</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.212972225132118</v>
+        <v>3.450653134049625</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-4.409276425334539</v>
+        <v>-2.857789548800827</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.212972209975918</v>
+        <v>3.450653118893425</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-4.409276425334539</v>
+        <v>-2.857789548800827</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.212972179663516</v>
+        <v>3.450653088581023</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-4.409276425334539</v>
+        <v>-2.857789548800827</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.212972164507315</v>
+        <v>3.450653073424823</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-4.409276425334539</v>
+        <v>-1.809504746419567</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.212972202397817</v>
+        <v>3.450653111315324</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383072</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.212972217554018</v>
+        <v>3.450653126471525</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7769695850834732</v>
+        <v>0.4870648583429532</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.212972209975918</v>
+        <v>3.450653118893425</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_1_000007.xlsx
+++ b/out/Attention-S4_repeat_1_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.006112316623330116</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.72</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.007054194808006287</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.4399999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.006033014506101608</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.009595311246812344</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.007803435437381268</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.006817225366830826</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.004167627543210983</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.005576305091381073</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.004852296784520149</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.006362100131809711</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.006569026038050652</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.005369743332266808</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.006449789740145206</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.006359230726957321</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.008322557434439659</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.006992306560277939</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.006799914874136448</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.005135741084814072</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.007269240915775299</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.005597889423370361</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.008089663460850716</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.009412776678800583</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.008026626892387867</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.005936066620051861</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.004924637265503407</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.005250128917396069</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.004380089230835438</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.006986458785831928</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.006967079825699329</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.006019618362188339</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.005705996416509151</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.005989234894514084</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.005670078098773956</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.005193265154957771</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.009538790211081505</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01099797151982784</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.007864393293857574</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.007146404124796391</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001218910279163392</v>
+        <v>-0.0001549058461502427</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.405223454710736</v>
+        <v>1.78583554918772</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.006986984983086586</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.812619282838985</v>
+        <v>3.574431829402426</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2107195254203982</v>
+        <v>0.2677940295027282</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.006737234070897102</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.826948769710943</v>
+        <v>2.321787350753424</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.2634679704750115</v>
+        <v>0.3348296714205644</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.006670490838587284</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.14319871717364</v>
+        <v>2.723695191651274</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.3776800862049891</v>
+        <v>0.4799765834096693</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0104762576520443</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.635239817932465</v>
+        <v>3.349007971857544</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.4040432295089283</v>
+        <v>0.5134802186497581</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01451993919909</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>3.065674024568085</v>
+        <v>3.896027286613095</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4282043845947278</v>
+        <v>0.5441855350372284</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01611333899199963</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>3.518070138195614</v>
+        <v>4.470956993080633</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.193240008828056</v>
+        <v>0.2455808107781548</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.009538212791085243</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.475991267850171</v>
+        <v>4.417480863582146</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.09332673509398459</v>
+        <v>0.1186043069563733</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.007326899096369743</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.469251869868549</v>
+        <v>4.40891609780406</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04446679786296001</v>
+        <v>0.05651142118971724</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.006709075532853603</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.464785842855833</v>
+        <v>4.403240444964288</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01317423205557543</v>
+        <v>0.01674393990492229</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.009414341300725937</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.446620613382627</v>
+        <v>4.380156708243582</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008712558995409792</v>
+        <v>0.01107338432264835</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01060812175273895</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.450866230787483</v>
+        <v>4.385553383028531</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.004457236457567908</v>
+        <v>0.005665533341778137</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01023604720830917</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.451061998268621</v>
+        <v>4.38580351489045</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002277103065622377</v>
+        <v>0.002895193618022969</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01211587525904179</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.451157320761765</v>
+        <v>4.38592600282335</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008533074960855064</v>
+        <v>0.001085671165660683</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01442850567400455</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.450584096326991</v>
+        <v>4.385198946905795</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004627783891056276</v>
+        <v>0.0005890043036261937</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01149164699018002</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.450655867469989</v>
+        <v>4.385291502274408</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002199085760080069</v>
+        <v>0.0002811027822009983</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0119025856256485</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.450633405661045</v>
+        <v>4.385264297620117</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001347216266757757</v>
+        <v>0.0001721119211383073</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01241584122180939</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.450682040067227</v>
+        <v>4.38532747434807</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>6.808521018146706e-05</v>
+        <v>8.764322417369065e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01130861975252628</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.450683407681526</v>
+        <v>4.385330591440431</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.996825957748122e-05</v>
+        <v>3.9959190885333e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.009744814597070217</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.450676212936765</v>
+        <v>4.385322778286423</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.802463479972881e-05</v>
+        <v>2.442036668854237e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.009443027898669243</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.450681279019888</v>
+        <v>4.385330640503748</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>5.490501498730158e-06</v>
+        <v>7.821724054003525e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.009154601022601128</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.450674220187132</v>
+        <v>4.385323010481095</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-8.825233700581938e-07</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.008390484377741814</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.450667987524883</v>
+        <v>4.385316366096433</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.009648198261857033</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.45066340161535</v>
+        <v>4.385311862193476</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01262598671019077</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.450657968483882</v>
+        <v>4.385306429062008</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01382286287844181</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.450652921862814</v>
+        <v>4.38530138244094</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01784373633563519</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.450653240143031</v>
+        <v>4.385301700721157</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01122813299298286</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7612199440383072</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.450654331389488</v>
+        <v>4.385302791967614</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.009150339290499687</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.809504746419567</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.450653641782352</v>
+        <v>4.385302102360478</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.005310676991939545</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.857789548800827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.450653672094754</v>
+        <v>4.38530213267288</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0004705358296632767</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.809504746419567</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.450653482642243</v>
+        <v>4.385301943220369</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.002468133345246315</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7612199440383072</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.450653535688947</v>
+        <v>4.385301996267073</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.004479542374610901</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.45065358873565</v>
+        <v>4.385302049313776</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01435519196093082</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.16</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.450653550845147</v>
+        <v>4.385302011423273</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.01750222966074944</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.45065342201744</v>
+        <v>4.385301882595567</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01376630831509829</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.450653278033533</v>
+        <v>4.385301738611659</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.004858976230025291</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.16</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.450653118893425</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.008381746709346771</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5612199440383071</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.450653171940127</v>
+        <v>4.385301632518253</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001036906614899635</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5612199440383071</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.450653118893425</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.00422259233891964</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7612199440383072</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.450653118893425</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.004529910162091255</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.450652937019016</v>
+        <v>4.385301397597142</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.0048325564712286</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.450653103737224</v>
+        <v>4.38530156431535</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.005459891632199287</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.450653300767834</v>
+        <v>4.385301761345961</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.001080403104424477</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.450653141627726</v>
+        <v>4.385301602205852</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01078455708920956</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.450653179518227</v>
+        <v>4.385301640096353</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.009765854105353355</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.450653376548838</v>
+        <v>4.385301837126963</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.004555070772767067</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.450653353814537</v>
+        <v>4.385301814392663</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.00371926836669445</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.450653202252528</v>
+        <v>4.385301662830654</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.00513034500181675</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.450653126471525</v>
+        <v>4.385301587049651</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.007800454273819923</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.16</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.450653224986831</v>
+        <v>4.385301685564957</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.009200423955917358</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.450653232564931</v>
+        <v>4.385301693143057</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01046071015298367</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.450653497798445</v>
+        <v>4.38530195837657</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01784655265510082</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.450653202252528</v>
+        <v>4.385301662830654</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01308142021298409</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.450653444751741</v>
+        <v>4.385301905329867</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01404031366109848</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.450653528110846</v>
+        <v>4.385301988688972</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.02028580941259861</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.450653361392638</v>
+        <v>4.385301821970764</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.007266910746693611</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2870648583429531</v>
+        <v>0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.450653550845147</v>
+        <v>4.385302011423273</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.0005775000900030136</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7612199440383072</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.450653202252528</v>
+        <v>4.385301662830654</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.002900084480643272</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.809504746419567</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.450652997643818</v>
+        <v>4.385301458221944</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.004491185769438744</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.809504746419567</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.450653111315324</v>
+        <v>4.38530157189345</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.0003365632146596909</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7612199440383072</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.450653126471525</v>
+        <v>4.385301587049651</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0008598808199167252</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.450652891550413</v>
+        <v>4.385301352128539</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.005614763125777245</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.450652952175216</v>
+        <v>4.385301412753342</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.009215621277689934</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.450652823347509</v>
+        <v>4.385301283925635</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.009507739916443825</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.450652959753317</v>
+        <v>4.385301420331443</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.009860483929514885</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.450653134049625</v>
+        <v>4.385301594627751</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.007139934226870537</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.450653278033533</v>
+        <v>4.385301738611659</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.004072019830346107</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.450653111315324</v>
+        <v>4.38530157189345</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.006929842755198479</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5612199440383071</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.450653103737224</v>
+        <v>4.38530156431535</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-5.182065069675446e-05</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7612199440383072</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.450652815769409</v>
+        <v>4.385301276347534</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.001646591350436211</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7612199440383072</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.45065283092561</v>
+        <v>4.385301291503736</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.003959732130169868</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.450653058268621</v>
+        <v>4.385301518846748</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.008755246177315712</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.2870648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.45065304311242</v>
+        <v>4.385301503690546</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.005298560485243797</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.450653149205826</v>
+        <v>4.385301609783952</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.002066018059849739</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.450652876394212</v>
+        <v>4.385301336972338</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.003474889323115349</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.4870648583429532</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.450652974909517</v>
+        <v>4.385301435487643</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.006783945485949516</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.450653126471525</v>
+        <v>4.385301587049651</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.008594533428549767</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.450653141627726</v>
+        <v>4.385301602205852</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.009571699425578117</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.450653118893425</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.007494313642382622</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7612199440383072</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.450653202252528</v>
+        <v>4.385301662830654</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.005813809111714363</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.809504746419567</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.450653300767834</v>
+        <v>4.385301761345961</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.008577654138207436</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.857789548800827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.450653134049625</v>
+        <v>4.385301594627751</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.00508602149784565</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.857789548800827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.450653118893425</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.00129137746989727</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.857789548800827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.450653088581023</v>
+        <v>4.385301549159148</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001421766355633736</v>
       </c>
       <c r="JB123" t="n">
-        <v>-2.857789548800827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.450653073424823</v>
+        <v>4.385301534002949</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002174625173211098</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.809504746419567</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.450653111315324</v>
+        <v>4.38530157189345</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.0008261930197477341</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7612199440383072</v>
+        <v>-0.4399999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.450653126471525</v>
+        <v>4.385301587049651</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.006681663915514946</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.4870648583429532</v>
+        <v>0.4400000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.450653118893425</v>
+        <v>4.385301579471551</v>
       </c>
     </row>
   </sheetData>
